--- a/data/trans_orig/P05A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A05-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122840</t>
+          <t>122372</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>164757</t>
+          <t>164104</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114833</t>
+          <t>115654</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154205</t>
+          <t>156554</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248106</t>
+          <t>248812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>307585</t>
+          <t>308991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>347941</t>
+          <t>351345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>401167</t>
+          <t>400689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>347140</t>
+          <t>347120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>398856</t>
+          <t>401248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>711268</t>
+          <t>710164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>783683</t>
+          <t>784483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,87%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152126</t>
+          <t>152670</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>197338</t>
+          <t>195797</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158199</t>
+          <t>158681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203631</t>
+          <t>204646</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>322089</t>
+          <t>321956</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>384816</t>
+          <t>385224</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>273666</t>
+          <t>272484</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>332535</t>
+          <t>334744</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224936</t>
+          <t>228269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>282504</t>
+          <t>287234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>519372</t>
+          <t>516418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>600684</t>
+          <t>599531</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>427586</t>
+          <t>431687</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>494675</t>
+          <t>494794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>474515</t>
+          <t>474715</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>539664</t>
+          <t>537639</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>920624</t>
+          <t>922583</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1011676</t>
+          <t>1015347</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167096</t>
+          <t>167664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221878</t>
+          <t>222582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>175613</t>
+          <t>176249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226404</t>
+          <t>229727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357816</t>
+          <t>361228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>433192</t>
+          <t>434137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>197287</t>
+          <t>196815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>248921</t>
+          <t>249154</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>219113</t>
+          <t>215077</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>269491</t>
+          <t>266391</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>431550</t>
+          <t>429754</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>501385</t>
+          <t>503697</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>329685</t>
+          <t>328394</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>384333</t>
+          <t>383672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>317020</t>
+          <t>313617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>367686</t>
+          <t>367493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>664972</t>
+          <t>660269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>732315</t>
+          <t>735087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>54,05%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81592</t>
+          <t>80605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119887</t>
+          <t>117573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82215</t>
+          <t>81024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116034</t>
+          <t>117575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171662</t>
+          <t>170733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221147</t>
+          <t>222672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>377039</t>
+          <t>373770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>434221</t>
+          <t>432938</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>386095</t>
+          <t>385986</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>448981</t>
+          <t>447140</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>780812</t>
+          <t>776507</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>867840</t>
+          <t>864589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>374779</t>
+          <t>374720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>430412</t>
+          <t>432748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>420485</t>
+          <t>420119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>485346</t>
+          <t>486095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>812853</t>
+          <t>814237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>898968</t>
+          <t>903035</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109788</t>
+          <t>108946</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153096</t>
+          <t>148982</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>143583</t>
+          <t>142729</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>196044</t>
+          <t>190589</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>264415</t>
+          <t>263159</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>327150</t>
+          <t>328305</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1022118</t>
+          <t>1020819</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1128639</t>
+          <t>1132825</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>995094</t>
+          <t>993982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1106850</t>
+          <t>1104160</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2045308</t>
+          <t>2048112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2201402</t>
+          <t>2193004</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1537180</t>
+          <t>1540307</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1660123</t>
+          <t>1657325</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1618564</t>
+          <t>1614570</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1729902</t>
+          <t>1729953</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3192424</t>
+          <t>3184798</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3363682</t>
+          <t>3357488</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,6%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>550722</t>
+          <t>549875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>639030</t>
+          <t>641177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>598882</t>
+          <t>603895</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>694705</t>
+          <t>690548</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1178313</t>
+          <t>1174107</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1300924</t>
+          <t>1310400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205726</t>
+          <t>204331</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>255888</t>
+          <t>256845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>196242</t>
+          <t>196231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>245118</t>
+          <t>243700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417260</t>
+          <t>418825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>491359</t>
+          <t>485054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>218087</t>
+          <t>218227</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270499</t>
+          <t>269330</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235781</t>
+          <t>237627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288720</t>
+          <t>288202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>472777</t>
+          <t>472093</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>544105</t>
+          <t>540543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>200858</t>
+          <t>201716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>249515</t>
+          <t>249977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>189002</t>
+          <t>187135</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>239796</t>
+          <t>239887</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>399206</t>
+          <t>400521</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>473863</t>
+          <t>471280</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345502</t>
+          <t>345635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410034</t>
+          <t>410552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364073</t>
+          <t>364475</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>428384</t>
+          <t>427460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>723972</t>
+          <t>733218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>817755</t>
+          <t>821396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402679</t>
+          <t>403588</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>468785</t>
+          <t>469598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>401940</t>
+          <t>402944</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>466650</t>
+          <t>470834</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>825111</t>
+          <t>829524</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>920159</t>
+          <t>921058</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172389</t>
+          <t>172775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>222032</t>
+          <t>225795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168098</t>
+          <t>166578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>220068</t>
+          <t>218014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>352643</t>
+          <t>351724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>426275</t>
+          <t>425814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>192618</t>
+          <t>197378</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>248908</t>
+          <t>251469</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>197815</t>
+          <t>196885</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>247595</t>
+          <t>251202</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>408482</t>
+          <t>406271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>482717</t>
+          <t>480743</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>321571</t>
+          <t>322962</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>380099</t>
+          <t>377508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>346109</t>
+          <t>345819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>401660</t>
+          <t>406124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>686186</t>
+          <t>684136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>764755</t>
+          <t>765097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156705</t>
+          <t>157594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206776</t>
+          <t>207526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152166</t>
+          <t>151846</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200896</t>
+          <t>201995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320305</t>
+          <t>321620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388036</t>
+          <t>393923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>244029</t>
+          <t>242771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>300558</t>
+          <t>299615</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>297571</t>
+          <t>298150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>358934</t>
+          <t>360330</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>559417</t>
+          <t>553640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>640391</t>
+          <t>639487</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389958</t>
+          <t>390817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>449561</t>
+          <t>451118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>412020</t>
+          <t>413005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>478894</t>
+          <t>476557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>820056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>908279</t>
+          <t>909554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>225428</t>
+          <t>225281</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>280860</t>
+          <t>278755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>246905</t>
+          <t>245027</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>305928</t>
+          <t>304711</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>486475</t>
+          <t>487162</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>566537</t>
+          <t>565431</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1044329</t>
+          <t>1045744</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1160263</t>
+          <t>1161026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1111024</t>
+          <t>1115924</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1230356</t>
+          <t>1226746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2181424</t>
+          <t>2186277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2353032</t>
+          <t>2346598</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1388495</t>
+          <t>1385916</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1510917</t>
+          <t>1512008</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1454052</t>
+          <t>1458119</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1578408</t>
+          <t>1569442</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2883046</t>
+          <t>2889649</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3060613</t>
+          <t>3064122</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>808419</t>
+          <t>798675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>915311</t>
+          <t>907549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>806088</t>
+          <t>806960</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>907061</t>
+          <t>913131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1643546</t>
+          <t>1637211</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1793226</t>
+          <t>1782199</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215001</t>
+          <t>214895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>266251</t>
+          <t>262675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>229978</t>
+          <t>227016</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279898</t>
+          <t>279238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>454701</t>
+          <t>458027</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>526679</t>
+          <t>527409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184872</t>
+          <t>184616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233268</t>
+          <t>229957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171078</t>
+          <t>172320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220865</t>
+          <t>221651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368714</t>
+          <t>367697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441663</t>
+          <t>436298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>200410</t>
+          <t>199417</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>248587</t>
+          <t>248427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>198971</t>
+          <t>194584</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>249085</t>
+          <t>247082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>414218</t>
+          <t>411894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>482827</t>
+          <t>480838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398964</t>
+          <t>401687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>464565</t>
+          <t>467921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416623</t>
+          <t>416293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482682</t>
+          <t>483162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>837985</t>
+          <t>837140</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930391</t>
+          <t>933398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>336034</t>
+          <t>333603</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399351</t>
+          <t>401429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>366961</t>
+          <t>366363</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>430111</t>
+          <t>428481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>719562</t>
+          <t>722508</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>811386</t>
+          <t>813169</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195080</t>
+          <t>191808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>249971</t>
+          <t>246300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167393</t>
+          <t>171321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>220024</t>
+          <t>224745</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>372953</t>
+          <t>373424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>446162</t>
+          <t>445735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>216737</t>
+          <t>217149</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>270085</t>
+          <t>267600</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>254013</t>
+          <t>255818</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>309923</t>
+          <t>311379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>484501</t>
+          <t>485944</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>560982</t>
+          <t>562534</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316738</t>
+          <t>314975</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>373976</t>
+          <t>369893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>307605</t>
+          <t>306643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361906</t>
+          <t>365626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>638002</t>
+          <t>640155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>721397</t>
+          <t>720905</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,9%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148546</t>
+          <t>149719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196718</t>
+          <t>194394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140497</t>
+          <t>140613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185945</t>
+          <t>190068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301082</t>
+          <t>302252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367598</t>
+          <t>370286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>318583</t>
+          <t>321458</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>380988</t>
+          <t>381379</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>389745</t>
+          <t>388564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>457626</t>
+          <t>453876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>730830</t>
+          <t>727527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>819905</t>
+          <t>816356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>383195</t>
+          <t>385098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>445551</t>
+          <t>446325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>394229</t>
+          <t>396772</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>458012</t>
+          <t>462134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>797799</t>
+          <t>797523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>887461</t>
+          <t>889749</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>145178</t>
+          <t>144626</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>194118</t>
+          <t>190591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164664</t>
+          <t>164583</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216950</t>
+          <t>214161</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>323078</t>
+          <t>321601</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>391271</t>
+          <t>390072</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1200614</t>
+          <t>1205618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1320159</t>
+          <t>1320986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1345036</t>
+          <t>1349350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1467578</t>
+          <t>1466807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2594422</t>
+          <t>2584107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2757183</t>
+          <t>2752705</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1275693</t>
+          <t>1284468</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1396378</t>
+          <t>1397976</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1296826</t>
+          <t>1293371</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1415686</t>
+          <t>1409948</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2595275</t>
+          <t>2605102</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2766095</t>
+          <t>2770010</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>732286</t>
+          <t>730207</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>831179</t>
+          <t>830573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>719000</t>
+          <t>719031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>818859</t>
+          <t>817253</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1480348</t>
+          <t>1473339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1618375</t>
+          <t>1621826</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>26954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>20188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41754</t>
+          <t>41389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>24242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45582</t>
+          <t>47002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25229</t>
+          <t>25608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47059</t>
+          <t>47247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55535</t>
+          <t>55190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83777</t>
+          <t>85710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>569956</t>
+          <t>566689</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>597506</t>
+          <t>596438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>662610</t>
+          <t>662908</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>688265</t>
+          <t>688565</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1241094</t>
+          <t>1241876</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1278137</t>
+          <t>1277538</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>25683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74877</t>
+          <t>75816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>40663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65624</t>
+          <t>67712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68427</t>
+          <t>67655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127925</t>
+          <t>128168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37313</t>
+          <t>37703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101908</t>
+          <t>100150</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67202</t>
+          <t>66968</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96624</t>
+          <t>96075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>94941</t>
+          <t>103614</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>181266</t>
+          <t>183127</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1024095</t>
+          <t>1024622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1127728</t>
+          <t>1128896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>804828</t>
+          <t>804714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>843230</t>
+          <t>841886</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1850190</t>
+          <t>1847548</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1982916</t>
+          <t>1987426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37462</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68847</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76932</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>582779</t>
+          <t>627809</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>124417</t>
+          <t>127969</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>762581</t>
+          <t>876375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115066</t>
+          <t>112605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>164460</t>
+          <t>163851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70301</t>
+          <t>66987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187945</t>
+          <t>188810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177965</t>
+          <t>171209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>329832</t>
+          <t>331095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486630</t>
+          <t>486949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>543108</t>
+          <t>543414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>278722</t>
+          <t>237993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>683710</t>
+          <t>679293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696387</t>
+          <t>601726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1203439</t>
+          <t>1198148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124444</t>
+          <t>123731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172964</t>
+          <t>171380</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141092</t>
+          <t>138016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>201329</t>
+          <t>200290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>283231</t>
+          <t>279710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>358553</t>
+          <t>355387</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152201</t>
+          <t>151344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203320</t>
+          <t>204804</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>218166</t>
+          <t>219248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>433901</t>
+          <t>464492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>388374</t>
+          <t>392154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>654824</t>
+          <t>643802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>571737</t>
+          <t>570747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>634596</t>
+          <t>633691</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>511736</t>
+          <t>499297</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>687399</t>
+          <t>688247</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078675</t>
+          <t>1090549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1297650</t>
+          <t>1297317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212815</t>
+          <t>207074</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306624</t>
+          <t>310529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317340</t>
+          <t>313415</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1101682</t>
+          <t>1111643</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>570529</t>
+          <t>568924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1474286</t>
+          <t>1466265</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>319702</t>
+          <t>335004</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>469221</t>
+          <t>473837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>448277</t>
+          <t>446845</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>735213</t>
+          <t>728721</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>826305</t>
+          <t>843507</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1164285</t>
+          <t>1158282</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2703469</t>
+          <t>2695481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2941023</t>
+          <t>2912984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2164050</t>
+          <t>2165341</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2853912</t>
+          <t>2848636</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4873202</t>
+          <t>4899739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5654232</t>
+          <t>5653815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">

--- a/data/trans_orig/P05A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A05-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122372</t>
+          <t>123203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>164104</t>
+          <t>165705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115654</t>
+          <t>115938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>156554</t>
+          <t>154368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248812</t>
+          <t>248291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>308991</t>
+          <t>306921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>351345</t>
+          <t>350745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>400689</t>
+          <t>401918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>347120</t>
+          <t>348012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401248</t>
+          <t>396758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>710164</t>
+          <t>713769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>784483</t>
+          <t>786090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152670</t>
+          <t>151586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>195797</t>
+          <t>194442</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158681</t>
+          <t>158730</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>204646</t>
+          <t>204218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>321956</t>
+          <t>324558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>385224</t>
+          <t>387411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>272484</t>
+          <t>274932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>334744</t>
+          <t>331671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228269</t>
+          <t>228100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>287234</t>
+          <t>283444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>516418</t>
+          <t>519123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>599531</t>
+          <t>598458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>431687</t>
+          <t>432015</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>494794</t>
+          <t>496003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>474715</t>
+          <t>474589</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>537639</t>
+          <t>537628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>922583</t>
+          <t>921914</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1015347</t>
+          <t>1012083</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167664</t>
+          <t>169943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>222582</t>
+          <t>219965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176249</t>
+          <t>175481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229727</t>
+          <t>229665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>361228</t>
+          <t>363156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>434137</t>
+          <t>434516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>196815</t>
+          <t>193554</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>249154</t>
+          <t>246236</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>215077</t>
+          <t>216174</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>266391</t>
+          <t>266433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>429754</t>
+          <t>430800</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>503697</t>
+          <t>497901</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>328394</t>
+          <t>328460</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>383672</t>
+          <t>383730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>313617</t>
+          <t>317765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>367493</t>
+          <t>367152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>660269</t>
+          <t>656442</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>735087</t>
+          <t>732540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,86%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80605</t>
+          <t>80810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117573</t>
+          <t>118169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>81757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>117575</t>
+          <t>116955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170733</t>
+          <t>171984</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>222672</t>
+          <t>227282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>373770</t>
+          <t>377475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>432938</t>
+          <t>437417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>385986</t>
+          <t>383256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>447140</t>
+          <t>445540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>776507</t>
+          <t>778971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>864589</t>
+          <t>863379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>374720</t>
+          <t>371641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>432748</t>
+          <t>429884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>420119</t>
+          <t>422484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486095</t>
+          <t>485093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>814237</t>
+          <t>811287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>903035</t>
+          <t>904229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108946</t>
+          <t>110240</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148982</t>
+          <t>151033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>142729</t>
+          <t>141985</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190589</t>
+          <t>192272</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>263159</t>
+          <t>265677</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>328305</t>
+          <t>328417</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1020819</t>
+          <t>1019364</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1132825</t>
+          <t>1121126</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>993982</t>
+          <t>998673</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1104160</t>
+          <t>1107392</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2048112</t>
+          <t>2046207</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2193004</t>
+          <t>2196875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1540307</t>
+          <t>1543587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1657325</t>
+          <t>1657056</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1614570</t>
+          <t>1615658</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1729953</t>
+          <t>1728967</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3184798</t>
+          <t>3192964</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3357488</t>
+          <t>3351784</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>549875</t>
+          <t>554313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>641177</t>
+          <t>639575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>603895</t>
+          <t>604021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>690548</t>
+          <t>691230</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1174107</t>
+          <t>1181043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1310400</t>
+          <t>1301389</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>204331</t>
+          <t>207159</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>256845</t>
+          <t>256652</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>196231</t>
+          <t>196513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243700</t>
+          <t>247927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>418825</t>
+          <t>414117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>485054</t>
+          <t>484246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>218227</t>
+          <t>215579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269330</t>
+          <t>271480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237627</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288202</t>
+          <t>290487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>472093</t>
+          <t>471204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>540543</t>
+          <t>543454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201716</t>
+          <t>201212</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>249977</t>
+          <t>251580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>187135</t>
+          <t>190718</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>239887</t>
+          <t>242736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>400521</t>
+          <t>401296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>471280</t>
+          <t>471355</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345635</t>
+          <t>345665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410552</t>
+          <t>410739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364475</t>
+          <t>366154</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>427460</t>
+          <t>427508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>733218</t>
+          <t>731360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821396</t>
+          <t>825550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>403588</t>
+          <t>403715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>469598</t>
+          <t>469269</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>402944</t>
+          <t>403378</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>470834</t>
+          <t>469137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>829524</t>
+          <t>822805</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>921058</t>
+          <t>918661</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172775</t>
+          <t>174483</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>225795</t>
+          <t>226603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166578</t>
+          <t>167259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>218014</t>
+          <t>216763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>351724</t>
+          <t>350991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>425814</t>
+          <t>425744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>197378</t>
+          <t>195271</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>251469</t>
+          <t>246695</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>196885</t>
+          <t>197701</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251202</t>
+          <t>249887</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>406271</t>
+          <t>402649</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>480743</t>
+          <t>479960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>322962</t>
+          <t>323555</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>377508</t>
+          <t>379100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>345819</t>
+          <t>347620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>406124</t>
+          <t>405788</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>684136</t>
+          <t>684891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>765097</t>
+          <t>766782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157594</t>
+          <t>160472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207526</t>
+          <t>209374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151846</t>
+          <t>150506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201995</t>
+          <t>199080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321620</t>
+          <t>323520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>393923</t>
+          <t>393134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>242771</t>
+          <t>240837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>299615</t>
+          <t>298575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>298150</t>
+          <t>297829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>360330</t>
+          <t>356569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>553640</t>
+          <t>556191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>639487</t>
+          <t>640057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>390817</t>
+          <t>388889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>451118</t>
+          <t>452339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>413005</t>
+          <t>411741</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>476557</t>
+          <t>476026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>820056</t>
+          <t>820435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>909554</t>
+          <t>915319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>225281</t>
+          <t>225089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>278755</t>
+          <t>282221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>245027</t>
+          <t>248077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>304711</t>
+          <t>306962</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>487162</t>
+          <t>488641</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>565431</t>
+          <t>567350</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1045744</t>
+          <t>1047007</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1161026</t>
+          <t>1165883</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1115924</t>
+          <t>1109950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1226746</t>
+          <t>1223368</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2186277</t>
+          <t>2189060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2346598</t>
+          <t>2349861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1385916</t>
+          <t>1398320</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1512008</t>
+          <t>1519295</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1458119</t>
+          <t>1456621</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1569442</t>
+          <t>1578633</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2889649</t>
+          <t>2883667</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3064122</t>
+          <t>3049725</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>798675</t>
+          <t>800392</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>907549</t>
+          <t>902620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>806960</t>
+          <t>802387</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>913131</t>
+          <t>909200</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1637211</t>
+          <t>1634358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1782199</t>
+          <t>1785675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>214895</t>
+          <t>216606</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>262675</t>
+          <t>264775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227016</t>
+          <t>228557</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279238</t>
+          <t>276115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>458027</t>
+          <t>456890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>527409</t>
+          <t>529362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184616</t>
+          <t>183939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229957</t>
+          <t>231646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172320</t>
+          <t>171972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221651</t>
+          <t>221298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367697</t>
+          <t>367033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436298</t>
+          <t>438697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199417</t>
+          <t>200729</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>248427</t>
+          <t>251343</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>194584</t>
+          <t>200119</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>247082</t>
+          <t>246394</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>411894</t>
+          <t>411274</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>480838</t>
+          <t>482699</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401687</t>
+          <t>403035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>467921</t>
+          <t>469465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416293</t>
+          <t>417973</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483162</t>
+          <t>482662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>837140</t>
+          <t>842471</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933398</t>
+          <t>931999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>333603</t>
+          <t>343027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>401429</t>
+          <t>400636</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>428481</t>
+          <t>430295</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>722508</t>
+          <t>722453</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>813169</t>
+          <t>809252</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191808</t>
+          <t>190146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>246300</t>
+          <t>243347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171321</t>
+          <t>168078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>224745</t>
+          <t>219269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>373424</t>
+          <t>377079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>445735</t>
+          <t>448197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>217149</t>
+          <t>216344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>267600</t>
+          <t>267247</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>255818</t>
+          <t>254204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>311379</t>
+          <t>307264</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>485944</t>
+          <t>488703</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562534</t>
+          <t>562172</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>314975</t>
+          <t>315035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>369893</t>
+          <t>370901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>306643</t>
+          <t>306343</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>365626</t>
+          <t>359520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>640155</t>
+          <t>638889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>720905</t>
+          <t>719796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149719</t>
+          <t>148653</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194394</t>
+          <t>192719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140613</t>
+          <t>141412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190068</t>
+          <t>190193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302252</t>
+          <t>302588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>370286</t>
+          <t>370260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>321458</t>
+          <t>321514</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>381379</t>
+          <t>382815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>388564</t>
+          <t>387861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>453876</t>
+          <t>453123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>727527</t>
+          <t>727618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>816356</t>
+          <t>812740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>385098</t>
+          <t>384377</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>446325</t>
+          <t>447741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>396772</t>
+          <t>395668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>462134</t>
+          <t>461049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>797523</t>
+          <t>798619</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>889749</t>
+          <t>885802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>144626</t>
+          <t>142423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>190591</t>
+          <t>190119</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164583</t>
+          <t>162055</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>214161</t>
+          <t>213544</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>321601</t>
+          <t>321458</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>390072</t>
+          <t>390735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1205618</t>
+          <t>1207646</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1320986</t>
+          <t>1327275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1349350</t>
+          <t>1347223</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1466807</t>
+          <t>1471061</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2584107</t>
+          <t>2596230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2752705</t>
+          <t>2754297</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1284468</t>
+          <t>1274584</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1397976</t>
+          <t>1392536</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1293371</t>
+          <t>1298858</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1409948</t>
+          <t>1412734</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2605102</t>
+          <t>2607243</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2770010</t>
+          <t>2765495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>730207</t>
+          <t>731615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>830573</t>
+          <t>835657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>719031</t>
+          <t>719651</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>817253</t>
+          <t>821941</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1473339</t>
+          <t>1478430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1621826</t>
+          <t>1618976</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>31597</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41389</t>
+          <t>44385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33711</t>
+          <t>36123</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24242</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47002</t>
+          <t>50421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35663</t>
+          <t>38868</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25608</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47247</t>
+          <t>50175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>69374</t>
+          <t>74991</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55190</t>
+          <t>60781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85710</t>
+          <t>91624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>585012</t>
+          <t>636660</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>566689</t>
+          <t>621069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>596438</t>
+          <t>649566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675719</t>
+          <t>679431</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>662908</t>
+          <t>666093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>688565</t>
+          <t>690406</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1260731</t>
+          <t>1316092</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1241876</t>
+          <t>1295041</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1277538</t>
+          <t>1334948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634021</t>
+          <t>689200</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634021</t>
+          <t>689200</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634021</t>
+          <t>689200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>724664</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>724664</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>724664</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1358686</t>
+          <t>1422680</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1358686</t>
+          <t>1422680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1358686</t>
+          <t>1422680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52853</t>
+          <t>60081</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25683</t>
+          <t>45332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75816</t>
+          <t>77883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>51334</t>
+          <t>57837</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40663</t>
+          <t>45558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67712</t>
+          <t>74328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104187</t>
+          <t>117918</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67655</t>
+          <t>98867</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>128168</t>
+          <t>142653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71495</t>
+          <t>87871</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37703</t>
+          <t>68675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100150</t>
+          <t>109603</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80409</t>
+          <t>90635</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66968</t>
+          <t>74157</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96075</t>
+          <t>105725</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>151904</t>
+          <t>178506</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103614</t>
+          <t>153370</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>183127</t>
+          <t>205387</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1068517</t>
+          <t>900965</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1024622</t>
+          <t>871539</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1128896</t>
+          <t>923649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>824796</t>
+          <t>920728</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>804714</t>
+          <t>900220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>841886</t>
+          <t>939908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1893312</t>
+          <t>1821694</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1847548</t>
+          <t>1787629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1987426</t>
+          <t>1854025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>956539</t>
+          <t>1069200</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>956539</t>
+          <t>1069200</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>956539</t>
+          <t>1069200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2149403</t>
+          <t>2118118</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2149403</t>
+          <t>2118118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2149403</t>
+          <t>2118118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51210</t>
+          <t>58988</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37445</t>
+          <t>43449</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68567</t>
+          <t>76004</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>271173</t>
+          <t>75287</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78812</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>627809</t>
+          <t>91611</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>322382</t>
+          <t>134275</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>127969</t>
+          <t>112723</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>876375</t>
+          <t>159645</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>137110</t>
+          <t>156891</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112605</t>
+          <t>132842</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163851</t>
+          <t>182724</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>139245</t>
+          <t>166906</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66987</t>
+          <t>144733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188810</t>
+          <t>187582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>276355</t>
+          <t>323797</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171209</t>
+          <t>290984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>331095</t>
+          <t>358051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>516196</t>
+          <t>586016</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486949</t>
+          <t>558723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>543414</t>
+          <t>613566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>522342</t>
+          <t>569395</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>237993</t>
+          <t>543141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679293</t>
+          <t>592637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1038537</t>
+          <t>1155411</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>601726</t>
+          <t>1114518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1198148</t>
+          <t>1190559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>932759</t>
+          <t>811588</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>932759</t>
+          <t>811588</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>932759</t>
+          <t>811588</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1637274</t>
+          <t>1613483</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1637274</t>
+          <t>1613483</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1637274</t>
+          <t>1613483</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>147054</t>
+          <t>159048</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123731</t>
+          <t>136107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171380</t>
+          <t>186062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>176444</t>
+          <t>196295</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138016</t>
+          <t>175553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200290</t>
+          <t>220867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>323497</t>
+          <t>355343</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>279710</t>
+          <t>323919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>355387</t>
+          <t>392092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177188</t>
+          <t>187479</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151344</t>
+          <t>162665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204804</t>
+          <t>217595</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>280925</t>
+          <t>240634</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>219248</t>
+          <t>217857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>464492</t>
+          <t>267255</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>458113</t>
+          <t>428113</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392154</t>
+          <t>396350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>643802</t>
+          <t>463367</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>602425</t>
+          <t>642416</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>570747</t>
+          <t>612386</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>633691</t>
+          <t>673471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>634976</t>
+          <t>678654</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>499297</t>
+          <t>649876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>688247</t>
+          <t>705646</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1237402</t>
+          <t>1321070</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1090549</t>
+          <t>1277768</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1297317</t>
+          <t>1362504</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1092345</t>
+          <t>1115582</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1092345</t>
+          <t>1115582</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1092345</t>
+          <t>1115582</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2019013</t>
+          <t>2104526</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2019013</t>
+          <t>2104526</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2019013</t>
+          <t>2104526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>266415</t>
+          <t>294534</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207074</t>
+          <t>260675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>310529</t>
+          <t>331370</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>512233</t>
+          <t>344599</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313415</t>
+          <t>310309</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1111643</t>
+          <t>376029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>778647</t>
+          <t>639134</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>568924</t>
+          <t>588594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1466265</t>
+          <t>687852</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>419503</t>
+          <t>468365</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>335004</t>
+          <t>424462</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>473837</t>
+          <t>519663</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>536242</t>
+          <t>537043</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>446845</t>
+          <t>500523</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>728721</t>
+          <t>579309</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>955746</t>
+          <t>1005407</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>843507</t>
+          <t>948171</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1158282</t>
+          <t>1067289</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2772151</t>
+          <t>2766058</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2695481</t>
+          <t>2708578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2912984</t>
+          <t>2821458</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2657832</t>
+          <t>2848207</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2165341</t>
+          <t>2798896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2848636</t>
+          <t>2892707</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5429983</t>
+          <t>5614265</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4899739</t>
+          <t>5536022</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5653815</t>
+          <t>5680289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3458069</t>
+          <t>3528957</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3458069</t>
+          <t>3528957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3458069</t>
+          <t>3528957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3706307</t>
+          <t>3729849</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3706307</t>
+          <t>3729849</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3706307</t>
+          <t>3729849</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7164376</t>
+          <t>7258806</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7164376</t>
+          <t>7258806</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7164376</t>
+          <t>7258806</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
